--- a/esyluban/examples/dev/DataTables/test/test_string.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_string.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.625" customWidth="1" style="5" min="3" max="4"/>
@@ -450,7 +450,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestString" &amp; value_type="test.TestString" &amp; read_schema_from_file="false" &amp; input="test/test_string.xlsx" &amp; output="test_tbteststring"</t>
+          <t>full_name="test.TbTestString" &amp; input="test/test_string.xlsx"</t>
         </is>
       </c>
     </row>
@@ -729,18 +729,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E1:G1"/>

--- a/esyluban/examples/dev/DataTables/test/test_string.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_string.xlsx
@@ -731,7 +731,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
